--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/ChbMstBondCreditRating001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/ChbMstBondCreditRating001.xlsx
@@ -1,182 +1,671 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView windowWidth="23040" windowHeight="8700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="评级机构枚举值" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="38">
   <si>
     <t>债券代码</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>评级对象</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>评级机构</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>评级类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>评级结果</t>
   </si>
   <si>
     <t>数据来源</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>评级日期(YYYY/MM/DD)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>01标准普尔评级服务公司</t>
-  </si>
-  <si>
-    <t>02中诚信国际信用评级有限责任公司</t>
-  </si>
-  <si>
-    <t>03上海远东资信评估有限公司</t>
-  </si>
-  <si>
-    <t>04上海新世纪资信评估投资服务有限公司</t>
-  </si>
-  <si>
-    <t>05联合资信评估有限公司</t>
-  </si>
-  <si>
-    <t>06大公国际资信评估有限公司</t>
-  </si>
-  <si>
-    <t>07联合信用评级有限公司</t>
-  </si>
-  <si>
-    <t>08辽宁省资信评估有限公司</t>
-  </si>
-  <si>
-    <t>09长城资信评估有限公司</t>
-  </si>
-  <si>
-    <t>10云南省资信评估事务所</t>
-  </si>
-  <si>
-    <t>11北京穆迪投资者服务有限公司</t>
-  </si>
-  <si>
-    <t>12福建省资信评级委员会</t>
-  </si>
-  <si>
-    <t>13中诚信证券评估有限公司</t>
-  </si>
-  <si>
-    <t>14鹏元资信评估有限公司</t>
-  </si>
-  <si>
-    <t>15穆迪投资者服务有限公司</t>
-  </si>
-  <si>
-    <t>16惠誉国际信用评级有限公司</t>
-  </si>
-  <si>
-    <t>17中国诚信信用管理股份有限公司</t>
-  </si>
-  <si>
-    <t>18中国证券监督管理委员会</t>
-  </si>
-  <si>
-    <t>19东方金诚国际信用评估有限公司</t>
-  </si>
-  <si>
-    <t>20中国证券业协会</t>
-  </si>
-  <si>
-    <t>21北京资信评级有限公司</t>
-  </si>
-  <si>
-    <t>22中债资信评估有限责任公司</t>
-  </si>
-  <si>
-    <t>23天津海泰信用服务有限公司</t>
-  </si>
-  <si>
-    <t>24中华信用评等公司</t>
-  </si>
-  <si>
-    <t>25联合信用管理有限公司</t>
-  </si>
-  <si>
-    <t>26南京中贝国际信用管理咨询有限公司</t>
-  </si>
-  <si>
-    <t>27穆迪投资者服务香港有限公司</t>
-  </si>
-  <si>
-    <t>28标准普尔香港有限公司</t>
-  </si>
-  <si>
-    <t>29上海资信有限公司</t>
-  </si>
-  <si>
-    <t>30株式会社日本格付研究所</t>
-  </si>
-  <si>
-    <t>31江苏安博尔信用评估有限公司</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标准普尔评级服务公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中诚信国际信用评级有限责任公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上海远东资信评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">04 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上海新世纪资信评估投资服务有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>联合资信评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大公国际资信评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>联合信用评级有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>辽宁省资信评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">09 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长城资信评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>云南省资信评估事务所</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>北京穆迪投资者服务有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>福建省资信评级委员会</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中诚信证券评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>鹏元资信评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>穆迪投资者服务有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>惠誉国际信用评级有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国诚信信用管理股份有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国证券监督管理委员会</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">19 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东方金诚国际信用评估有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国证券业协会</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">21 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>北京资信评级有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">22 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中债资信评估有限责任公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">23 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>天津海泰信用服务有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">24 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中华信用评等公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>联合信用管理有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>南京中贝国际信用管理咨询有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">27 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>穆迪投资者服务香港有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标准普尔香港有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上海资信有限公司</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>株式会社日本格付研究所</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>江苏安博尔信用评估有限公司</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,7 +674,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -197,12 +734,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBF7FF"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -212,63 +869,330 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color rgb="FFE6E6E6"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color rgb="FFE6E6E6"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 5" xfId="1"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 5" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -317,7 +1241,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -352,7 +1276,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -555,242 +1479,392 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="7" width="17.125" customWidth="1"/>
+    <col min="1" max="7" width="17.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="21.6" spans="1:7">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="G4" s="5"/>
+    <row r="4" spans="7:7">
+      <c r="G4" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F3:F1048576">
+      <formula1>"01内部,02外部"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2">
+      <formula1>"01 内部,02 外部"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"01 主体评级,02 债项评级,93 担保人评级"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+      <formula1>评级机构枚举值!$A:$A</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
       <formula1>"01 长期, 02 短期"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576">
-      <formula1>"01内部,02外部"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"01 AAA+, 02 AAA, 03 AAA-, 04 AA+,05 AA,06 AA-,07 A+,08 A,09 A-,10 A-1,11A-2,12 A-3,13 BBB+,14 BBB,15 BBB-,16 BB+,17 BB,18 BB-,19 B+,20 B,21 B-,22 CCC+,23 CCC,24 CCC-,25 CC+,26 CC,27 CC-,28 C+,29 C,30 C-,31 D"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>评级机构枚举值!$A:$A</xm:f>
-          </x14:formula1>
-          <xm:sqref>C1:C1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A62"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="42.625" customWidth="1"/>
+    <col min="1" max="1" width="42.6296296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>